--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_40.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_40.xlsx
@@ -471,45 +471,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1608</v>
+        <v>96481</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Manuela da Rosa</t>
+          <t>Lorenzo Nogueira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45092</v>
+        <v>45101</v>
       </c>
       <c r="G2" t="n">
-        <v>5873.78</v>
+        <v>10484.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64146</v>
+        <v>7409</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yasmin Campos</t>
+          <t>Sr. Thiago da Paz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,80 +518,80 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45085</v>
+        <v>45079</v>
       </c>
       <c r="G3" t="n">
-        <v>5289.62</v>
+        <v>11449.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74885</v>
+        <v>99076</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emanuel Carvalho</t>
+          <t>Sra. Ana Beatriz Gomes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45086</v>
+        <v>45097</v>
       </c>
       <c r="G4" t="n">
-        <v>9555.700000000001</v>
+        <v>4781.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4562</v>
+        <v>35889</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sr. Benjamin Costela</t>
+          <t>Maitê Farias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45096</v>
+        <v>45078</v>
       </c>
       <c r="G5" t="n">
-        <v>3243.78</v>
+        <v>8595.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68418</v>
+        <v>68531</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Benício Cardoso</t>
+          <t>Catarina Santos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,55 +601,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45093</v>
+        <v>45096</v>
       </c>
       <c r="G6" t="n">
-        <v>8305.110000000001</v>
+        <v>9757.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85652</v>
+        <v>45564</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Isabella da Mota</t>
+          <t>João Gabriel Fernandes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45106</v>
+        <v>45100</v>
       </c>
       <c r="G7" t="n">
-        <v>3231.64</v>
+        <v>7290.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2936</v>
+        <v>18754</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cauã Moraes</t>
+          <t>Alice Cunha</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,89 +659,89 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45090</v>
+        <v>45103</v>
       </c>
       <c r="G8" t="n">
-        <v>6634.01</v>
+        <v>9986.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13884</v>
+        <v>78031</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eloah Gonçalves</t>
+          <t>Luana Barbosa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45080</v>
+        <v>45105</v>
       </c>
       <c r="G9" t="n">
-        <v>9796.030000000001</v>
+        <v>9540.299999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47874</v>
+        <v>42948</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Leonardo Fernandes</t>
+          <t>Benjamin Castro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45101</v>
+        <v>45092</v>
       </c>
       <c r="G10" t="n">
-        <v>11375.85</v>
+        <v>5646.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94628</v>
+        <v>71688</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gabriel Farias</t>
+          <t>Vitória Castro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45092</v>
+        <v>45093</v>
       </c>
       <c r="G11" t="n">
-        <v>2858.77</v>
+        <v>12082.79</v>
       </c>
     </row>
   </sheetData>
